--- a/main/ig/StructureDefinition-fr-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:12:30+00:00</t>
+    <t>2026-07-22T09:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:23:07+00:00</t>
+    <t>2026-07-23T06:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T06:55:30+00:00</t>
+    <t>2026-07-23T07:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T07:15:05+00:00</t>
+    <t>2026-07-23T09:42:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
